--- a/files/九龙-长沙湾-翠雅山.xlsx
+++ b/files/九龙-长沙湾-翠雅山.xlsx
@@ -1441,11 +1441,11 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2496</v>
+        <v>2493</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -1453,15 +1453,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H18" s="5" t="n">
+        <v>44179200</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>17721</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -2720,7 +2716,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>1 套</t>
+          <t>2 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -2730,7 +2726,7 @@
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>27 套</t>
+          <t>26 套</t>
         </is>
       </c>
     </row>
@@ -3073,12 +3069,12 @@
       <c r="Q9" s="16" t="inlineStr"/>
       <c r="R9" s="16" t="inlineStr"/>
       <c r="S9" s="16" t="inlineStr"/>
-      <c r="T9" s="17" t="inlineStr">
-        <is>
-          <t>3 | 2496呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
+      <c r="T9" s="18" t="inlineStr">
+        <is>
+          <t>3 | 2493呎 (4+房)
+$4,418万
+$17,721/呎
+(已售)</t>
         </is>
       </c>
       <c r="U9" s="16" t="inlineStr"/>

--- a/files/九龙-长沙湾-翠雅山.xlsx
+++ b/files/九龙-长沙湾-翠雅山.xlsx
@@ -8,9 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座 销控表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -113,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -178,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,45 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -608,7 +473,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -1254,7 +1119,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1450,7 +1315,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -2422,1145 +2287,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>翠雅山 - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>PHA</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>PHA | 1352呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr"/>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>3 | 1352呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr"/>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>2 | 1352呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr"/>
-      <c r="E8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>G/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>1 | 1381呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr"/>
-      <c r="D9" s="16" t="inlineStr"/>
-      <c r="E9" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:AC14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-    <col width="18" customWidth="1" min="24" max="24"/>
-    <col width="18" customWidth="1" min="25" max="25"/>
-    <col width="18" customWidth="1" min="26" max="26"/>
-    <col width="18" customWidth="1" min="27" max="27"/>
-    <col width="18" customWidth="1" min="28" max="28"/>
-    <col width="18" customWidth="1" min="29" max="29"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>翠雅山 - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>28 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>26 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y5" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t>PHA</t>
-        </is>
-      </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>PHB</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>PHC</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr">
-        <is>
-          <t>PHD</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>B4/F</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>1 | 1463呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr"/>
-      <c r="E6" s="16" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr"/>
-      <c r="G6" s="16" t="inlineStr"/>
-      <c r="H6" s="16" t="inlineStr"/>
-      <c r="I6" s="16" t="inlineStr"/>
-      <c r="J6" s="16" t="inlineStr"/>
-      <c r="K6" s="16" t="inlineStr"/>
-      <c r="L6" s="17" t="inlineStr">
-        <is>
-          <t>2 | 1824呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M6" s="16" t="inlineStr"/>
-      <c r="N6" s="16" t="inlineStr"/>
-      <c r="O6" s="16" t="inlineStr"/>
-      <c r="P6" s="16" t="inlineStr"/>
-      <c r="Q6" s="16" t="inlineStr"/>
-      <c r="R6" s="16" t="inlineStr"/>
-      <c r="S6" s="16" t="inlineStr"/>
-      <c r="T6" s="16" t="inlineStr"/>
-      <c r="U6" s="16" t="inlineStr"/>
-      <c r="V6" s="16" t="inlineStr"/>
-      <c r="W6" s="16" t="inlineStr"/>
-      <c r="X6" s="16" t="inlineStr"/>
-      <c r="Y6" s="16" t="inlineStr"/>
-      <c r="Z6" s="16" t="inlineStr"/>
-      <c r="AA6" s="16" t="inlineStr"/>
-      <c r="AB6" s="16" t="inlineStr"/>
-      <c r="AC6" s="16" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr"/>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr"/>
-      <c r="F7" s="16" t="inlineStr"/>
-      <c r="G7" s="16" t="inlineStr"/>
-      <c r="H7" s="16" t="inlineStr"/>
-      <c r="I7" s="16" t="inlineStr"/>
-      <c r="J7" s="16" t="inlineStr"/>
-      <c r="K7" s="16" t="inlineStr"/>
-      <c r="L7" s="16" t="inlineStr"/>
-      <c r="M7" s="16" t="inlineStr"/>
-      <c r="N7" s="16" t="inlineStr"/>
-      <c r="O7" s="16" t="inlineStr"/>
-      <c r="P7" s="16" t="inlineStr"/>
-      <c r="Q7" s="16" t="inlineStr"/>
-      <c r="R7" s="16" t="inlineStr"/>
-      <c r="S7" s="16" t="inlineStr"/>
-      <c r="T7" s="16" t="inlineStr"/>
-      <c r="U7" s="16" t="inlineStr"/>
-      <c r="V7" s="16" t="inlineStr"/>
-      <c r="W7" s="16" t="inlineStr"/>
-      <c r="X7" s="16" t="inlineStr"/>
-      <c r="Y7" s="16" t="inlineStr"/>
-      <c r="Z7" s="17" t="inlineStr">
-        <is>
-          <t>PHA | 1679呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="AA7" s="17" t="inlineStr">
-        <is>
-          <t>PHB | 1867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="AB7" s="17" t="inlineStr">
-        <is>
-          <t>PHC | 1883呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="AC7" s="17" t="inlineStr">
-        <is>
-          <t>PHD | 1513呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>B3/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr"/>
-      <c r="C8" s="16" t="inlineStr"/>
-      <c r="D8" s="16" t="inlineStr"/>
-      <c r="E8" s="16" t="inlineStr"/>
-      <c r="F8" s="16" t="inlineStr"/>
-      <c r="G8" s="16" t="inlineStr"/>
-      <c r="H8" s="16" t="inlineStr"/>
-      <c r="I8" s="16" t="inlineStr"/>
-      <c r="J8" s="16" t="inlineStr"/>
-      <c r="K8" s="16" t="inlineStr"/>
-      <c r="L8" s="16" t="inlineStr"/>
-      <c r="M8" s="16" t="inlineStr"/>
-      <c r="N8" s="16" t="inlineStr"/>
-      <c r="O8" s="16" t="inlineStr"/>
-      <c r="P8" s="16" t="inlineStr"/>
-      <c r="Q8" s="16" t="inlineStr"/>
-      <c r="R8" s="16" t="inlineStr"/>
-      <c r="S8" s="16" t="inlineStr"/>
-      <c r="T8" s="16" t="inlineStr"/>
-      <c r="U8" s="17" t="inlineStr">
-        <is>
-          <t>5 | 1866呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="V8" s="18" t="inlineStr">
-        <is>
-          <t>6 | 1879呎 (4+房)
-$3,046万
-$16,209/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="W8" s="17" t="inlineStr">
-        <is>
-          <t>7 | 1499呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="X8" s="16" t="inlineStr"/>
-      <c r="Y8" s="16" t="inlineStr"/>
-      <c r="Z8" s="16" t="inlineStr"/>
-      <c r="AA8" s="16" t="inlineStr"/>
-      <c r="AB8" s="16" t="inlineStr"/>
-      <c r="AC8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>B2&amp;B3/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr"/>
-      <c r="C9" s="16" t="inlineStr"/>
-      <c r="D9" s="16" t="inlineStr"/>
-      <c r="E9" s="16" t="inlineStr"/>
-      <c r="F9" s="16" t="inlineStr"/>
-      <c r="G9" s="16" t="inlineStr"/>
-      <c r="H9" s="16" t="inlineStr"/>
-      <c r="I9" s="16" t="inlineStr"/>
-      <c r="J9" s="16" t="inlineStr"/>
-      <c r="K9" s="16" t="inlineStr"/>
-      <c r="L9" s="16" t="inlineStr"/>
-      <c r="M9" s="16" t="inlineStr"/>
-      <c r="N9" s="16" t="inlineStr"/>
-      <c r="O9" s="16" t="inlineStr"/>
-      <c r="P9" s="16" t="inlineStr"/>
-      <c r="Q9" s="16" t="inlineStr"/>
-      <c r="R9" s="16" t="inlineStr"/>
-      <c r="S9" s="16" t="inlineStr"/>
-      <c r="T9" s="18" t="inlineStr">
-        <is>
-          <t>3 | 2493呎 (4+房)
-$4,418万
-$17,721/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="U9" s="16" t="inlineStr"/>
-      <c r="V9" s="16" t="inlineStr"/>
-      <c r="W9" s="16" t="inlineStr"/>
-      <c r="X9" s="16" t="inlineStr"/>
-      <c r="Y9" s="16" t="inlineStr"/>
-      <c r="Z9" s="16" t="inlineStr"/>
-      <c r="AA9" s="16" t="inlineStr"/>
-      <c r="AB9" s="16" t="inlineStr"/>
-      <c r="AC9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr"/>
-      <c r="C10" s="16" t="inlineStr"/>
-      <c r="D10" s="16" t="inlineStr"/>
-      <c r="E10" s="16" t="inlineStr"/>
-      <c r="F10" s="16" t="inlineStr"/>
-      <c r="G10" s="16" t="inlineStr"/>
-      <c r="H10" s="16" t="inlineStr"/>
-      <c r="I10" s="16" t="inlineStr"/>
-      <c r="J10" s="16" t="inlineStr"/>
-      <c r="K10" s="16" t="inlineStr"/>
-      <c r="L10" s="16" t="inlineStr"/>
-      <c r="M10" s="16" t="inlineStr"/>
-      <c r="N10" s="16" t="inlineStr"/>
-      <c r="O10" s="16" t="inlineStr"/>
-      <c r="P10" s="17" t="inlineStr">
-        <is>
-          <t>23 | 1675呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q10" s="17" t="inlineStr">
-        <is>
-          <t>25 | 1867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="R10" s="17" t="inlineStr">
-        <is>
-          <t>26 | 1883呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="S10" s="17" t="inlineStr">
-        <is>
-          <t>27 | 1513呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="T10" s="16" t="inlineStr"/>
-      <c r="U10" s="16" t="inlineStr"/>
-      <c r="V10" s="16" t="inlineStr"/>
-      <c r="W10" s="16" t="inlineStr"/>
-      <c r="X10" s="16" t="inlineStr"/>
-      <c r="Y10" s="16" t="inlineStr"/>
-      <c r="Z10" s="16" t="inlineStr"/>
-      <c r="AA10" s="16" t="inlineStr"/>
-      <c r="AB10" s="16" t="inlineStr"/>
-      <c r="AC10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>B2/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr"/>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>10 | 1535呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr"/>
-      <c r="E11" s="16" t="inlineStr"/>
-      <c r="F11" s="16" t="inlineStr"/>
-      <c r="G11" s="16" t="inlineStr"/>
-      <c r="H11" s="16" t="inlineStr"/>
-      <c r="I11" s="16" t="inlineStr"/>
-      <c r="J11" s="16" t="inlineStr"/>
-      <c r="K11" s="16" t="inlineStr"/>
-      <c r="L11" s="16" t="inlineStr"/>
-      <c r="M11" s="16" t="inlineStr"/>
-      <c r="N11" s="16" t="inlineStr"/>
-      <c r="O11" s="16" t="inlineStr"/>
-      <c r="P11" s="16" t="inlineStr"/>
-      <c r="Q11" s="16" t="inlineStr"/>
-      <c r="R11" s="16" t="inlineStr"/>
-      <c r="S11" s="16" t="inlineStr"/>
-      <c r="T11" s="16" t="inlineStr"/>
-      <c r="U11" s="16" t="inlineStr"/>
-      <c r="V11" s="16" t="inlineStr"/>
-      <c r="W11" s="16" t="inlineStr"/>
-      <c r="X11" s="17" t="inlineStr">
-        <is>
-          <t>8 | 1896呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Y11" s="17" t="inlineStr">
-        <is>
-          <t>9 | 1880呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Z11" s="16" t="inlineStr"/>
-      <c r="AA11" s="16" t="inlineStr"/>
-      <c r="AB11" s="16" t="inlineStr"/>
-      <c r="AC11" s="16" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr"/>
-      <c r="C12" s="16" t="inlineStr"/>
-      <c r="D12" s="16" t="inlineStr"/>
-      <c r="E12" s="16" t="inlineStr"/>
-      <c r="F12" s="16" t="inlineStr"/>
-      <c r="G12" s="16" t="inlineStr"/>
-      <c r="H12" s="16" t="inlineStr"/>
-      <c r="I12" s="16" t="inlineStr"/>
-      <c r="J12" s="16" t="inlineStr"/>
-      <c r="K12" s="17" t="inlineStr">
-        <is>
-          <t>19 | 1676呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L12" s="16" t="inlineStr"/>
-      <c r="M12" s="17" t="inlineStr">
-        <is>
-          <t>20 | 1867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N12" s="17" t="inlineStr">
-        <is>
-          <t>21 | 1883呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O12" s="17" t="inlineStr">
-        <is>
-          <t>22 | 1513呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P12" s="16" t="inlineStr"/>
-      <c r="Q12" s="16" t="inlineStr"/>
-      <c r="R12" s="16" t="inlineStr"/>
-      <c r="S12" s="16" t="inlineStr"/>
-      <c r="T12" s="16" t="inlineStr"/>
-      <c r="U12" s="16" t="inlineStr"/>
-      <c r="V12" s="16" t="inlineStr"/>
-      <c r="W12" s="16" t="inlineStr"/>
-      <c r="X12" s="16" t="inlineStr"/>
-      <c r="Y12" s="16" t="inlineStr"/>
-      <c r="Z12" s="16" t="inlineStr"/>
-      <c r="AA12" s="16" t="inlineStr"/>
-      <c r="AB12" s="16" t="inlineStr"/>
-      <c r="AC12" s="16" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>B1/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr"/>
-      <c r="C13" s="16" t="inlineStr"/>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>11 | 1968呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>12 | 1879呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>13 | 1565呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr"/>
-      <c r="H13" s="16" t="inlineStr"/>
-      <c r="I13" s="16" t="inlineStr"/>
-      <c r="J13" s="16" t="inlineStr"/>
-      <c r="K13" s="16" t="inlineStr"/>
-      <c r="L13" s="16" t="inlineStr"/>
-      <c r="M13" s="16" t="inlineStr"/>
-      <c r="N13" s="16" t="inlineStr"/>
-      <c r="O13" s="16" t="inlineStr"/>
-      <c r="P13" s="16" t="inlineStr"/>
-      <c r="Q13" s="16" t="inlineStr"/>
-      <c r="R13" s="16" t="inlineStr"/>
-      <c r="S13" s="16" t="inlineStr"/>
-      <c r="T13" s="16" t="inlineStr"/>
-      <c r="U13" s="16" t="inlineStr"/>
-      <c r="V13" s="16" t="inlineStr"/>
-      <c r="W13" s="16" t="inlineStr"/>
-      <c r="X13" s="16" t="inlineStr"/>
-      <c r="Y13" s="16" t="inlineStr"/>
-      <c r="Z13" s="16" t="inlineStr"/>
-      <c r="AA13" s="16" t="inlineStr"/>
-      <c r="AB13" s="16" t="inlineStr"/>
-      <c r="AC13" s="16" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>G/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr"/>
-      <c r="C14" s="16" t="inlineStr"/>
-      <c r="D14" s="16" t="inlineStr"/>
-      <c r="E14" s="16" t="inlineStr"/>
-      <c r="F14" s="16" t="inlineStr"/>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>15 | 1355呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>16 | 1989呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>17 | 1955呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J14" s="17" t="inlineStr">
-        <is>
-          <t>18 | 1557呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K14" s="16" t="inlineStr"/>
-      <c r="L14" s="16" t="inlineStr"/>
-      <c r="M14" s="16" t="inlineStr"/>
-      <c r="N14" s="16" t="inlineStr"/>
-      <c r="O14" s="16" t="inlineStr"/>
-      <c r="P14" s="16" t="inlineStr"/>
-      <c r="Q14" s="16" t="inlineStr"/>
-      <c r="R14" s="16" t="inlineStr"/>
-      <c r="S14" s="16" t="inlineStr"/>
-      <c r="T14" s="16" t="inlineStr"/>
-      <c r="U14" s="16" t="inlineStr"/>
-      <c r="V14" s="16" t="inlineStr"/>
-      <c r="W14" s="16" t="inlineStr"/>
-      <c r="X14" s="16" t="inlineStr"/>
-      <c r="Y14" s="16" t="inlineStr"/>
-      <c r="Z14" s="16" t="inlineStr"/>
-      <c r="AA14" s="16" t="inlineStr"/>
-      <c r="AB14" s="16" t="inlineStr"/>
-      <c r="AC14" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AC1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>翠雅山 - 3座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>PHA</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>PHA | 1506呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr"/>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>2 | 1514呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>1 | 1485呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr"/>
-      <c r="D8" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-长沙湾-翠雅山.xlsx
+++ b/files/九龙-长沙湾-翠雅山.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +44,90 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +138,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +219,57 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +646,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -2287,4 +2459,1145 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>PHA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>PHA | 1352呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>3 | 1352呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>2 | 1352呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>1 | 1381呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AC13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N4" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="O4" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P4" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Q4" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R4" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="S4" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="T4" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U4" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V4" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W4" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X4" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y4" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z4" s="19" t="inlineStr">
+        <is>
+          <t>PHA</t>
+        </is>
+      </c>
+      <c r="AA4" s="19" t="inlineStr">
+        <is>
+          <t>PHB</t>
+        </is>
+      </c>
+      <c r="AB4" s="19" t="inlineStr">
+        <is>
+          <t>PHC</t>
+        </is>
+      </c>
+      <c r="AC4" s="19" t="inlineStr">
+        <is>
+          <t>PHD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>1 | 1463呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="20" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr"/>
+      <c r="I5" s="20" t="inlineStr"/>
+      <c r="J5" s="20" t="inlineStr"/>
+      <c r="K5" s="20" t="inlineStr"/>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t>2 | 1824呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M5" s="20" t="inlineStr"/>
+      <c r="N5" s="20" t="inlineStr"/>
+      <c r="O5" s="20" t="inlineStr"/>
+      <c r="P5" s="20" t="inlineStr"/>
+      <c r="Q5" s="20" t="inlineStr"/>
+      <c r="R5" s="20" t="inlineStr"/>
+      <c r="S5" s="20" t="inlineStr"/>
+      <c r="T5" s="20" t="inlineStr"/>
+      <c r="U5" s="20" t="inlineStr"/>
+      <c r="V5" s="20" t="inlineStr"/>
+      <c r="W5" s="20" t="inlineStr"/>
+      <c r="X5" s="20" t="inlineStr"/>
+      <c r="Y5" s="20" t="inlineStr"/>
+      <c r="Z5" s="20" t="inlineStr"/>
+      <c r="AA5" s="20" t="inlineStr"/>
+      <c r="AB5" s="20" t="inlineStr"/>
+      <c r="AC5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+      <c r="K6" s="20" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr"/>
+      <c r="M6" s="20" t="inlineStr"/>
+      <c r="N6" s="20" t="inlineStr"/>
+      <c r="O6" s="20" t="inlineStr"/>
+      <c r="P6" s="20" t="inlineStr"/>
+      <c r="Q6" s="20" t="inlineStr"/>
+      <c r="R6" s="20" t="inlineStr"/>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="20" t="inlineStr"/>
+      <c r="U6" s="21" t="inlineStr">
+        <is>
+          <t>5 | 1866呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="V6" s="22" t="inlineStr">
+        <is>
+          <t>6 | 1879呎 (4+房)
+$3046万
+$16,209/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="W6" s="21" t="inlineStr">
+        <is>
+          <t>7 | 1499呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="X6" s="20" t="inlineStr"/>
+      <c r="Y6" s="20" t="inlineStr"/>
+      <c r="Z6" s="20" t="inlineStr"/>
+      <c r="AA6" s="20" t="inlineStr"/>
+      <c r="AB6" s="20" t="inlineStr"/>
+      <c r="AC6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr"/>
+      <c r="K7" s="20" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr"/>
+      <c r="M7" s="20" t="inlineStr"/>
+      <c r="N7" s="20" t="inlineStr"/>
+      <c r="O7" s="20" t="inlineStr"/>
+      <c r="P7" s="20" t="inlineStr"/>
+      <c r="Q7" s="20" t="inlineStr"/>
+      <c r="R7" s="20" t="inlineStr"/>
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="20" t="inlineStr"/>
+      <c r="U7" s="20" t="inlineStr"/>
+      <c r="V7" s="20" t="inlineStr"/>
+      <c r="W7" s="20" t="inlineStr"/>
+      <c r="X7" s="20" t="inlineStr"/>
+      <c r="Y7" s="20" t="inlineStr"/>
+      <c r="Z7" s="21" t="inlineStr">
+        <is>
+          <t>PHA | 1679呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="AA7" s="21" t="inlineStr">
+        <is>
+          <t>PHB | 1867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="AB7" s="21" t="inlineStr">
+        <is>
+          <t>PHC | 1883呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="AC7" s="21" t="inlineStr">
+        <is>
+          <t>PHD | 1513呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr"/>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+      <c r="F8" s="20" t="inlineStr"/>
+      <c r="G8" s="20" t="inlineStr"/>
+      <c r="H8" s="20" t="inlineStr"/>
+      <c r="I8" s="20" t="inlineStr"/>
+      <c r="J8" s="20" t="inlineStr"/>
+      <c r="K8" s="20" t="inlineStr"/>
+      <c r="L8" s="20" t="inlineStr"/>
+      <c r="M8" s="20" t="inlineStr"/>
+      <c r="N8" s="20" t="inlineStr"/>
+      <c r="O8" s="20" t="inlineStr"/>
+      <c r="P8" s="21" t="inlineStr">
+        <is>
+          <t>23 | 1675呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q8" s="21" t="inlineStr">
+        <is>
+          <t>25 | 1867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="R8" s="21" t="inlineStr">
+        <is>
+          <t>26 | 1883呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="S8" s="21" t="inlineStr">
+        <is>
+          <t>27 | 1513呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="T8" s="20" t="inlineStr"/>
+      <c r="U8" s="20" t="inlineStr"/>
+      <c r="V8" s="20" t="inlineStr"/>
+      <c r="W8" s="20" t="inlineStr"/>
+      <c r="X8" s="20" t="inlineStr"/>
+      <c r="Y8" s="20" t="inlineStr"/>
+      <c r="Z8" s="20" t="inlineStr"/>
+      <c r="AA8" s="20" t="inlineStr"/>
+      <c r="AB8" s="20" t="inlineStr"/>
+      <c r="AC8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>10 | 1535呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="inlineStr"/>
+      <c r="H9" s="20" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+      <c r="K9" s="20" t="inlineStr"/>
+      <c r="L9" s="20" t="inlineStr"/>
+      <c r="M9" s="20" t="inlineStr"/>
+      <c r="N9" s="20" t="inlineStr"/>
+      <c r="O9" s="20" t="inlineStr"/>
+      <c r="P9" s="20" t="inlineStr"/>
+      <c r="Q9" s="20" t="inlineStr"/>
+      <c r="R9" s="20" t="inlineStr"/>
+      <c r="S9" s="20" t="inlineStr"/>
+      <c r="T9" s="20" t="inlineStr"/>
+      <c r="U9" s="20" t="inlineStr"/>
+      <c r="V9" s="20" t="inlineStr"/>
+      <c r="W9" s="20" t="inlineStr"/>
+      <c r="X9" s="21" t="inlineStr">
+        <is>
+          <t>8 | 1896呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Y9" s="21" t="inlineStr">
+        <is>
+          <t>9 | 1880呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Z9" s="20" t="inlineStr"/>
+      <c r="AA9" s="20" t="inlineStr"/>
+      <c r="AB9" s="20" t="inlineStr"/>
+      <c r="AC9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>B2&amp;B3</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr"/>
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr"/>
+      <c r="H10" s="20" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr"/>
+      <c r="J10" s="20" t="inlineStr"/>
+      <c r="K10" s="20" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr"/>
+      <c r="M10" s="20" t="inlineStr"/>
+      <c r="N10" s="20" t="inlineStr"/>
+      <c r="O10" s="20" t="inlineStr"/>
+      <c r="P10" s="20" t="inlineStr"/>
+      <c r="Q10" s="20" t="inlineStr"/>
+      <c r="R10" s="20" t="inlineStr"/>
+      <c r="S10" s="20" t="inlineStr"/>
+      <c r="T10" s="22" t="inlineStr">
+        <is>
+          <t>3 | 2493呎 (4+房)
+$4418万
+$17,721/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="U10" s="20" t="inlineStr"/>
+      <c r="V10" s="20" t="inlineStr"/>
+      <c r="W10" s="20" t="inlineStr"/>
+      <c r="X10" s="20" t="inlineStr"/>
+      <c r="Y10" s="20" t="inlineStr"/>
+      <c r="Z10" s="20" t="inlineStr"/>
+      <c r="AA10" s="20" t="inlineStr"/>
+      <c r="AB10" s="20" t="inlineStr"/>
+      <c r="AC10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr"/>
+      <c r="C11" s="20" t="inlineStr"/>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>11 | 1968呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>12 | 1879呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>13 | 1565呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr"/>
+      <c r="H11" s="20" t="inlineStr"/>
+      <c r="I11" s="20" t="inlineStr"/>
+      <c r="J11" s="20" t="inlineStr"/>
+      <c r="K11" s="20" t="inlineStr"/>
+      <c r="L11" s="20" t="inlineStr"/>
+      <c r="M11" s="20" t="inlineStr"/>
+      <c r="N11" s="20" t="inlineStr"/>
+      <c r="O11" s="20" t="inlineStr"/>
+      <c r="P11" s="20" t="inlineStr"/>
+      <c r="Q11" s="20" t="inlineStr"/>
+      <c r="R11" s="20" t="inlineStr"/>
+      <c r="S11" s="20" t="inlineStr"/>
+      <c r="T11" s="20" t="inlineStr"/>
+      <c r="U11" s="20" t="inlineStr"/>
+      <c r="V11" s="20" t="inlineStr"/>
+      <c r="W11" s="20" t="inlineStr"/>
+      <c r="X11" s="20" t="inlineStr"/>
+      <c r="Y11" s="20" t="inlineStr"/>
+      <c r="Z11" s="20" t="inlineStr"/>
+      <c r="AA11" s="20" t="inlineStr"/>
+      <c r="AB11" s="20" t="inlineStr"/>
+      <c r="AC11" s="20" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr"/>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="20" t="inlineStr"/>
+      <c r="H12" s="20" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+      <c r="K12" s="21" t="inlineStr">
+        <is>
+          <t>19 | 1676呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L12" s="20" t="inlineStr"/>
+      <c r="M12" s="21" t="inlineStr">
+        <is>
+          <t>20 | 1867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t>21 | 1883呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O12" s="21" t="inlineStr">
+        <is>
+          <t>22 | 1513呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P12" s="20" t="inlineStr"/>
+      <c r="Q12" s="20" t="inlineStr"/>
+      <c r="R12" s="20" t="inlineStr"/>
+      <c r="S12" s="20" t="inlineStr"/>
+      <c r="T12" s="20" t="inlineStr"/>
+      <c r="U12" s="20" t="inlineStr"/>
+      <c r="V12" s="20" t="inlineStr"/>
+      <c r="W12" s="20" t="inlineStr"/>
+      <c r="X12" s="20" t="inlineStr"/>
+      <c r="Y12" s="20" t="inlineStr"/>
+      <c r="Z12" s="20" t="inlineStr"/>
+      <c r="AA12" s="20" t="inlineStr"/>
+      <c r="AB12" s="20" t="inlineStr"/>
+      <c r="AC12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr"/>
+      <c r="C13" s="20" t="inlineStr"/>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>15 | 1355呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>16 | 1989呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>17 | 1955呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t>18 | 1557呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K13" s="20" t="inlineStr"/>
+      <c r="L13" s="20" t="inlineStr"/>
+      <c r="M13" s="20" t="inlineStr"/>
+      <c r="N13" s="20" t="inlineStr"/>
+      <c r="O13" s="20" t="inlineStr"/>
+      <c r="P13" s="20" t="inlineStr"/>
+      <c r="Q13" s="20" t="inlineStr"/>
+      <c r="R13" s="20" t="inlineStr"/>
+      <c r="S13" s="20" t="inlineStr"/>
+      <c r="T13" s="20" t="inlineStr"/>
+      <c r="U13" s="20" t="inlineStr"/>
+      <c r="V13" s="20" t="inlineStr"/>
+      <c r="W13" s="20" t="inlineStr"/>
+      <c r="X13" s="20" t="inlineStr"/>
+      <c r="Y13" s="20" t="inlineStr"/>
+      <c r="Z13" s="20" t="inlineStr"/>
+      <c r="AA13" s="20" t="inlineStr"/>
+      <c r="AB13" s="20" t="inlineStr"/>
+      <c r="AC13" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>PHA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>PHA | 1506呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>2 | 1514呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>1 | 1485呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-长沙湾-翠雅山.xlsx
+++ b/files/九龙-长沙湾-翠雅山.xlsx
@@ -646,7 +646,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -2966,7 +2966,7 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr"/>
@@ -2988,41 +2988,48 @@
       <c r="R6" s="20" t="inlineStr"/>
       <c r="S6" s="20" t="inlineStr"/>
       <c r="T6" s="20" t="inlineStr"/>
-      <c r="U6" s="21" t="inlineStr">
-        <is>
-          <t>5 | 1866呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="V6" s="22" t="inlineStr">
-        <is>
-          <t>6 | 1879呎 (4+房)
-$3046万
-$16,209/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="W6" s="21" t="inlineStr">
-        <is>
-          <t>7 | 1499呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="U6" s="20" t="inlineStr"/>
+      <c r="V6" s="20" t="inlineStr"/>
+      <c r="W6" s="20" t="inlineStr"/>
       <c r="X6" s="20" t="inlineStr"/>
       <c r="Y6" s="20" t="inlineStr"/>
-      <c r="Z6" s="20" t="inlineStr"/>
-      <c r="AA6" s="20" t="inlineStr"/>
-      <c r="AB6" s="20" t="inlineStr"/>
-      <c r="AC6" s="20" t="inlineStr"/>
+      <c r="Z6" s="21" t="inlineStr">
+        <is>
+          <t>PHA | 1679呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="AA6" s="21" t="inlineStr">
+        <is>
+          <t>PHB | 1867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="AB6" s="21" t="inlineStr">
+        <is>
+          <t>PHC | 1883呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="AC6" s="21" t="inlineStr">
+        <is>
+          <t>PHD | 1513呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="B7" s="20" t="inlineStr"/>
@@ -3044,48 +3051,41 @@
       <c r="R7" s="20" t="inlineStr"/>
       <c r="S7" s="20" t="inlineStr"/>
       <c r="T7" s="20" t="inlineStr"/>
-      <c r="U7" s="20" t="inlineStr"/>
-      <c r="V7" s="20" t="inlineStr"/>
-      <c r="W7" s="20" t="inlineStr"/>
+      <c r="U7" s="21" t="inlineStr">
+        <is>
+          <t>5 | 1866呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="V7" s="22" t="inlineStr">
+        <is>
+          <t>6 | 1879呎 (4+房)
+$3046万
+$16,209/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="W7" s="21" t="inlineStr">
+        <is>
+          <t>7 | 1499呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="X7" s="20" t="inlineStr"/>
       <c r="Y7" s="20" t="inlineStr"/>
-      <c r="Z7" s="21" t="inlineStr">
-        <is>
-          <t>PHA | 1679呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="AA7" s="21" t="inlineStr">
-        <is>
-          <t>PHB | 1867呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="AB7" s="21" t="inlineStr">
-        <is>
-          <t>PHC | 1883呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="AC7" s="21" t="inlineStr">
-        <is>
-          <t>PHD | 1513呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="Z7" s="20" t="inlineStr"/>
+      <c r="AA7" s="20" t="inlineStr"/>
+      <c r="AB7" s="20" t="inlineStr"/>
+      <c r="AC7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>B2&amp;B3</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr"/>
@@ -3102,39 +3102,18 @@
       <c r="M8" s="20" t="inlineStr"/>
       <c r="N8" s="20" t="inlineStr"/>
       <c r="O8" s="20" t="inlineStr"/>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t>23 | 1675呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q8" s="21" t="inlineStr">
-        <is>
-          <t>25 | 1867呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="R8" s="21" t="inlineStr">
-        <is>
-          <t>26 | 1883呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="S8" s="21" t="inlineStr">
-        <is>
-          <t>27 | 1513呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="T8" s="20" t="inlineStr"/>
+      <c r="P8" s="20" t="inlineStr"/>
+      <c r="Q8" s="20" t="inlineStr"/>
+      <c r="R8" s="20" t="inlineStr"/>
+      <c r="S8" s="20" t="inlineStr"/>
+      <c r="T8" s="22" t="inlineStr">
+        <is>
+          <t>3 | 2493呎 (4+房)
+$4418万
+$17,721/呎
+(26年-07月)</t>
+        </is>
+      </c>
       <c r="U8" s="20" t="inlineStr"/>
       <c r="V8" s="20" t="inlineStr"/>
       <c r="W8" s="20" t="inlineStr"/>
@@ -3204,7 +3183,7 @@
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>B2&amp;B3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr"/>
@@ -3221,18 +3200,39 @@
       <c r="M10" s="20" t="inlineStr"/>
       <c r="N10" s="20" t="inlineStr"/>
       <c r="O10" s="20" t="inlineStr"/>
-      <c r="P10" s="20" t="inlineStr"/>
-      <c r="Q10" s="20" t="inlineStr"/>
-      <c r="R10" s="20" t="inlineStr"/>
-      <c r="S10" s="20" t="inlineStr"/>
-      <c r="T10" s="22" t="inlineStr">
-        <is>
-          <t>3 | 2493呎 (4+房)
-$4418万
-$17,721/呎
-(26年-07月)</t>
-        </is>
-      </c>
+      <c r="P10" s="21" t="inlineStr">
+        <is>
+          <t>23 | 1675呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q10" s="21" t="inlineStr">
+        <is>
+          <t>25 | 1867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="R10" s="21" t="inlineStr">
+        <is>
+          <t>26 | 1883呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="S10" s="21" t="inlineStr">
+        <is>
+          <t>27 | 1513呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="T10" s="20" t="inlineStr"/>
       <c r="U10" s="20" t="inlineStr"/>
       <c r="V10" s="20" t="inlineStr"/>
       <c r="W10" s="20" t="inlineStr"/>
@@ -3246,44 +3246,51 @@
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B11" s="20" t="inlineStr"/>
       <c r="C11" s="20" t="inlineStr"/>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>11 | 1968呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="inlineStr">
-        <is>
-          <t>12 | 1879呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t>13 | 1565呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="D11" s="20" t="inlineStr"/>
+      <c r="E11" s="20" t="inlineStr"/>
+      <c r="F11" s="20" t="inlineStr"/>
       <c r="G11" s="20" t="inlineStr"/>
       <c r="H11" s="20" t="inlineStr"/>
       <c r="I11" s="20" t="inlineStr"/>
       <c r="J11" s="20" t="inlineStr"/>
-      <c r="K11" s="20" t="inlineStr"/>
+      <c r="K11" s="21" t="inlineStr">
+        <is>
+          <t>19 | 1676呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="L11" s="20" t="inlineStr"/>
-      <c r="M11" s="20" t="inlineStr"/>
-      <c r="N11" s="20" t="inlineStr"/>
-      <c r="O11" s="20" t="inlineStr"/>
+      <c r="M11" s="21" t="inlineStr">
+        <is>
+          <t>20 | 1867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N11" s="21" t="inlineStr">
+        <is>
+          <t>21 | 1883呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O11" s="21" t="inlineStr">
+        <is>
+          <t>22 | 1513呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="P11" s="20" t="inlineStr"/>
       <c r="Q11" s="20" t="inlineStr"/>
       <c r="R11" s="20" t="inlineStr"/>
@@ -3302,51 +3309,44 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr"/>
       <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
-      <c r="E12" s="20" t="inlineStr"/>
-      <c r="F12" s="20" t="inlineStr"/>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>11 | 1968呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>12 | 1879呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>13 | 1565呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="G12" s="20" t="inlineStr"/>
       <c r="H12" s="20" t="inlineStr"/>
       <c r="I12" s="20" t="inlineStr"/>
       <c r="J12" s="20" t="inlineStr"/>
-      <c r="K12" s="21" t="inlineStr">
-        <is>
-          <t>19 | 1676呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="K12" s="20" t="inlineStr"/>
       <c r="L12" s="20" t="inlineStr"/>
-      <c r="M12" s="21" t="inlineStr">
-        <is>
-          <t>20 | 1867呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="N12" s="21" t="inlineStr">
-        <is>
-          <t>21 | 1883呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="O12" s="21" t="inlineStr">
-        <is>
-          <t>22 | 1513呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="M12" s="20" t="inlineStr"/>
+      <c r="N12" s="20" t="inlineStr"/>
+      <c r="O12" s="20" t="inlineStr"/>
       <c r="P12" s="20" t="inlineStr"/>
       <c r="Q12" s="20" t="inlineStr"/>
       <c r="R12" s="20" t="inlineStr"/>

--- a/files/九龙-长沙湾-翠雅山.xlsx
+++ b/files/九龙-长沙湾-翠雅山.xlsx
@@ -636,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -649,6 +649,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -706,6 +710,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -756,6 +780,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -806,6 +850,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -856,6 +920,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -906,6 +990,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -956,6 +1060,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1006,6 +1130,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1056,6 +1200,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1106,6 +1270,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1156,6 +1340,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1206,6 +1410,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1256,6 +1480,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1302,6 +1546,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1352,6 +1616,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1402,6 +1686,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1452,6 +1756,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1498,6 +1822,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1548,6 +1892,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1598,6 +1962,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1648,6 +2032,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1698,6 +2102,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1748,6 +2172,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1798,6 +2242,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1848,6 +2312,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1898,6 +2382,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1948,6 +2452,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1998,6 +2522,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2048,6 +2592,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2098,6 +2662,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2148,6 +2732,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2198,6 +2802,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2248,6 +2872,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2298,6 +2942,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2348,6 +3012,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2398,6 +3082,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2448,13 +3152,33 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -3064,7 +3788,7 @@
           <t>6 | 1879呎 (4+房)
 $3046万
 $16,209/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="W7" s="21" t="inlineStr">
@@ -3111,7 +3835,7 @@
           <t>3 | 2493呎 (4+房)
 $4418万
 $17,721/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="U8" s="20" t="inlineStr"/>
@@ -3127,18 +3851,11 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>10 | 1535呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C9" s="20" t="inlineStr"/>
       <c r="D9" s="20" t="inlineStr"/>
       <c r="E9" s="20" t="inlineStr"/>
       <c r="F9" s="20" t="inlineStr"/>
@@ -3151,30 +3868,44 @@
       <c r="M9" s="20" t="inlineStr"/>
       <c r="N9" s="20" t="inlineStr"/>
       <c r="O9" s="20" t="inlineStr"/>
-      <c r="P9" s="20" t="inlineStr"/>
-      <c r="Q9" s="20" t="inlineStr"/>
-      <c r="R9" s="20" t="inlineStr"/>
-      <c r="S9" s="20" t="inlineStr"/>
+      <c r="P9" s="21" t="inlineStr">
+        <is>
+          <t>23 | 1675呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q9" s="21" t="inlineStr">
+        <is>
+          <t>25 | 1867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="R9" s="21" t="inlineStr">
+        <is>
+          <t>26 | 1883呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="S9" s="21" t="inlineStr">
+        <is>
+          <t>27 | 1513呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="T9" s="20" t="inlineStr"/>
       <c r="U9" s="20" t="inlineStr"/>
       <c r="V9" s="20" t="inlineStr"/>
       <c r="W9" s="20" t="inlineStr"/>
-      <c r="X9" s="21" t="inlineStr">
-        <is>
-          <t>8 | 1896呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="Y9" s="21" t="inlineStr">
-        <is>
-          <t>9 | 1880呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="X9" s="20" t="inlineStr"/>
+      <c r="Y9" s="20" t="inlineStr"/>
       <c r="Z9" s="20" t="inlineStr"/>
       <c r="AA9" s="20" t="inlineStr"/>
       <c r="AB9" s="20" t="inlineStr"/>
@@ -3183,11 +3914,18 @@
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr"/>
-      <c r="C10" s="20" t="inlineStr"/>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>10 | 1535呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="D10" s="20" t="inlineStr"/>
       <c r="E10" s="20" t="inlineStr"/>
       <c r="F10" s="20" t="inlineStr"/>
@@ -3200,44 +3938,30 @@
       <c r="M10" s="20" t="inlineStr"/>
       <c r="N10" s="20" t="inlineStr"/>
       <c r="O10" s="20" t="inlineStr"/>
-      <c r="P10" s="21" t="inlineStr">
-        <is>
-          <t>23 | 1675呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q10" s="21" t="inlineStr">
-        <is>
-          <t>25 | 1867呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="R10" s="21" t="inlineStr">
-        <is>
-          <t>26 | 1883呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="S10" s="21" t="inlineStr">
-        <is>
-          <t>27 | 1513呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="P10" s="20" t="inlineStr"/>
+      <c r="Q10" s="20" t="inlineStr"/>
+      <c r="R10" s="20" t="inlineStr"/>
+      <c r="S10" s="20" t="inlineStr"/>
       <c r="T10" s="20" t="inlineStr"/>
       <c r="U10" s="20" t="inlineStr"/>
       <c r="V10" s="20" t="inlineStr"/>
       <c r="W10" s="20" t="inlineStr"/>
-      <c r="X10" s="20" t="inlineStr"/>
-      <c r="Y10" s="20" t="inlineStr"/>
+      <c r="X10" s="21" t="inlineStr">
+        <is>
+          <t>8 | 1896呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Y10" s="21" t="inlineStr">
+        <is>
+          <t>9 | 1880呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="Z10" s="20" t="inlineStr"/>
       <c r="AA10" s="20" t="inlineStr"/>
       <c r="AB10" s="20" t="inlineStr"/>
@@ -3246,51 +3970,44 @@
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B11" s="20" t="inlineStr"/>
       <c r="C11" s="20" t="inlineStr"/>
-      <c r="D11" s="20" t="inlineStr"/>
-      <c r="E11" s="20" t="inlineStr"/>
-      <c r="F11" s="20" t="inlineStr"/>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>11 | 1968呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>12 | 1879呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>13 | 1565呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="G11" s="20" t="inlineStr"/>
       <c r="H11" s="20" t="inlineStr"/>
       <c r="I11" s="20" t="inlineStr"/>
       <c r="J11" s="20" t="inlineStr"/>
-      <c r="K11" s="21" t="inlineStr">
-        <is>
-          <t>19 | 1676呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="K11" s="20" t="inlineStr"/>
       <c r="L11" s="20" t="inlineStr"/>
-      <c r="M11" s="21" t="inlineStr">
-        <is>
-          <t>20 | 1867呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="N11" s="21" t="inlineStr">
-        <is>
-          <t>21 | 1883呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="O11" s="21" t="inlineStr">
-        <is>
-          <t>22 | 1513呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="M11" s="20" t="inlineStr"/>
+      <c r="N11" s="20" t="inlineStr"/>
+      <c r="O11" s="20" t="inlineStr"/>
       <c r="P11" s="20" t="inlineStr"/>
       <c r="Q11" s="20" t="inlineStr"/>
       <c r="R11" s="20" t="inlineStr"/>
@@ -3309,44 +4026,51 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr"/>
       <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t>11 | 1968呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>12 | 1879呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t>13 | 1565呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
       <c r="G12" s="20" t="inlineStr"/>
       <c r="H12" s="20" t="inlineStr"/>
       <c r="I12" s="20" t="inlineStr"/>
       <c r="J12" s="20" t="inlineStr"/>
-      <c r="K12" s="20" t="inlineStr"/>
+      <c r="K12" s="21" t="inlineStr">
+        <is>
+          <t>19 | 1676呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="L12" s="20" t="inlineStr"/>
-      <c r="M12" s="20" t="inlineStr"/>
-      <c r="N12" s="20" t="inlineStr"/>
-      <c r="O12" s="20" t="inlineStr"/>
+      <c r="M12" s="21" t="inlineStr">
+        <is>
+          <t>20 | 1867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t>21 | 1883呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O12" s="21" t="inlineStr">
+        <is>
+          <t>22 | 1513呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="P12" s="20" t="inlineStr"/>
       <c r="Q12" s="20" t="inlineStr"/>
       <c r="R12" s="20" t="inlineStr"/>

--- a/files/九龙-长沙湾-翠雅山.xlsx
+++ b/files/九龙-长沙湾-翠雅山.xlsx
@@ -3851,11 +3851,18 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="20" t="inlineStr"/>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>10 | 1535呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="D9" s="20" t="inlineStr"/>
       <c r="E9" s="20" t="inlineStr"/>
       <c r="F9" s="20" t="inlineStr"/>
@@ -3868,44 +3875,30 @@
       <c r="M9" s="20" t="inlineStr"/>
       <c r="N9" s="20" t="inlineStr"/>
       <c r="O9" s="20" t="inlineStr"/>
-      <c r="P9" s="21" t="inlineStr">
-        <is>
-          <t>23 | 1675呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q9" s="21" t="inlineStr">
-        <is>
-          <t>25 | 1867呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="R9" s="21" t="inlineStr">
-        <is>
-          <t>26 | 1883呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="S9" s="21" t="inlineStr">
-        <is>
-          <t>27 | 1513呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="P9" s="20" t="inlineStr"/>
+      <c r="Q9" s="20" t="inlineStr"/>
+      <c r="R9" s="20" t="inlineStr"/>
+      <c r="S9" s="20" t="inlineStr"/>
       <c r="T9" s="20" t="inlineStr"/>
       <c r="U9" s="20" t="inlineStr"/>
       <c r="V9" s="20" t="inlineStr"/>
       <c r="W9" s="20" t="inlineStr"/>
-      <c r="X9" s="20" t="inlineStr"/>
-      <c r="Y9" s="20" t="inlineStr"/>
+      <c r="X9" s="21" t="inlineStr">
+        <is>
+          <t>8 | 1896呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Y9" s="21" t="inlineStr">
+        <is>
+          <t>9 | 1880呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="Z9" s="20" t="inlineStr"/>
       <c r="AA9" s="20" t="inlineStr"/>
       <c r="AB9" s="20" t="inlineStr"/>
@@ -3914,18 +3907,11 @@
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr"/>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>10 | 1535呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C10" s="20" t="inlineStr"/>
       <c r="D10" s="20" t="inlineStr"/>
       <c r="E10" s="20" t="inlineStr"/>
       <c r="F10" s="20" t="inlineStr"/>
@@ -3938,30 +3924,44 @@
       <c r="M10" s="20" t="inlineStr"/>
       <c r="N10" s="20" t="inlineStr"/>
       <c r="O10" s="20" t="inlineStr"/>
-      <c r="P10" s="20" t="inlineStr"/>
-      <c r="Q10" s="20" t="inlineStr"/>
-      <c r="R10" s="20" t="inlineStr"/>
-      <c r="S10" s="20" t="inlineStr"/>
+      <c r="P10" s="21" t="inlineStr">
+        <is>
+          <t>23 | 1675呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q10" s="21" t="inlineStr">
+        <is>
+          <t>25 | 1867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="R10" s="21" t="inlineStr">
+        <is>
+          <t>26 | 1883呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="S10" s="21" t="inlineStr">
+        <is>
+          <t>27 | 1513呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="T10" s="20" t="inlineStr"/>
       <c r="U10" s="20" t="inlineStr"/>
       <c r="V10" s="20" t="inlineStr"/>
       <c r="W10" s="20" t="inlineStr"/>
-      <c r="X10" s="21" t="inlineStr">
-        <is>
-          <t>8 | 1896呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="Y10" s="21" t="inlineStr">
-        <is>
-          <t>9 | 1880呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="X10" s="20" t="inlineStr"/>
+      <c r="Y10" s="20" t="inlineStr"/>
       <c r="Z10" s="20" t="inlineStr"/>
       <c r="AA10" s="20" t="inlineStr"/>
       <c r="AB10" s="20" t="inlineStr"/>
@@ -3970,44 +3970,51 @@
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B11" s="20" t="inlineStr"/>
       <c r="C11" s="20" t="inlineStr"/>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>11 | 1968呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="inlineStr">
-        <is>
-          <t>12 | 1879呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t>13 | 1565呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="D11" s="20" t="inlineStr"/>
+      <c r="E11" s="20" t="inlineStr"/>
+      <c r="F11" s="20" t="inlineStr"/>
       <c r="G11" s="20" t="inlineStr"/>
       <c r="H11" s="20" t="inlineStr"/>
       <c r="I11" s="20" t="inlineStr"/>
       <c r="J11" s="20" t="inlineStr"/>
-      <c r="K11" s="20" t="inlineStr"/>
+      <c r="K11" s="21" t="inlineStr">
+        <is>
+          <t>19 | 1676呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="L11" s="20" t="inlineStr"/>
-      <c r="M11" s="20" t="inlineStr"/>
-      <c r="N11" s="20" t="inlineStr"/>
-      <c r="O11" s="20" t="inlineStr"/>
+      <c r="M11" s="21" t="inlineStr">
+        <is>
+          <t>20 | 1867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N11" s="21" t="inlineStr">
+        <is>
+          <t>21 | 1883呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O11" s="21" t="inlineStr">
+        <is>
+          <t>22 | 1513呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="P11" s="20" t="inlineStr"/>
       <c r="Q11" s="20" t="inlineStr"/>
       <c r="R11" s="20" t="inlineStr"/>
@@ -4026,51 +4033,44 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr"/>
       <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
-      <c r="E12" s="20" t="inlineStr"/>
-      <c r="F12" s="20" t="inlineStr"/>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>11 | 1968呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>12 | 1879呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>13 | 1565呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="G12" s="20" t="inlineStr"/>
       <c r="H12" s="20" t="inlineStr"/>
       <c r="I12" s="20" t="inlineStr"/>
       <c r="J12" s="20" t="inlineStr"/>
-      <c r="K12" s="21" t="inlineStr">
-        <is>
-          <t>19 | 1676呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="K12" s="20" t="inlineStr"/>
       <c r="L12" s="20" t="inlineStr"/>
-      <c r="M12" s="21" t="inlineStr">
-        <is>
-          <t>20 | 1867呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="N12" s="21" t="inlineStr">
-        <is>
-          <t>21 | 1883呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="O12" s="21" t="inlineStr">
-        <is>
-          <t>22 | 1513呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="M12" s="20" t="inlineStr"/>
+      <c r="N12" s="20" t="inlineStr"/>
+      <c r="O12" s="20" t="inlineStr"/>
       <c r="P12" s="20" t="inlineStr"/>
       <c r="Q12" s="20" t="inlineStr"/>
       <c r="R12" s="20" t="inlineStr"/>
